--- a/naver-place-crawler/results_health/계양구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/계양구_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="Q2" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="R2" t="n">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,41 +646,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>와이투짐 계양점 24시</t>
+          <t>테이스트피트니스 헬스&amp;PT 24시 계양구청점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>y2gym12@naver.com</t>
+          <t>tastegy@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1396-2001</t>
+          <t>0507-1460-0265</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 임학동로 38 와이투짐 계양점 24시</t>
+          <t>인천광역시 계양구 오조산로57번길 7 성림프라자 6층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sThOVtmh</t>
+          <t>http://pf.kakao.com/_fbwxbn</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>831</v>
+        <v>2073</v>
       </c>
       <c r="Q3" t="n">
-        <v>819</v>
+        <v>273</v>
       </c>
       <c r="R3" t="n">
-        <v>1650</v>
+        <v>2346</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,56 +730,56 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>36208586</t>
+          <t>1987764939</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36208586</t>
+          <t>https://m.place.naver.com/place/1987764939</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>테이스트피트니스 헬스&amp;PT 24시 계양구청점</t>
+          <t>짐710 헬스장 PT 계양구청점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>tastegy@naver.com</t>
+          <t>junwon092300@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1460-0265</t>
+          <t>0507-1444-9971</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 오조산로57번길 7 성림프라자 6층</t>
+          <t>인천광역시 계양구 오조산로 53 미소지움메디칼빌딩 6층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_fbwxbn</t>
+          <t>https://blog.naver.com/junwon092300</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2070</v>
+        <v>1012</v>
       </c>
       <c r="Q4" t="n">
-        <v>265</v>
+        <v>884</v>
       </c>
       <c r="R4" t="n">
-        <v>2335</v>
+        <v>1896</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,51 +824,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1987764939</t>
+          <t>1400484331</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1987764939</t>
+          <t>https://m.place.naver.com/place/1400484331</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>랩스휘트니스 헬스 PT 계산역점</t>
+          <t>짐베이피트니스 헬스 PT 계산역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rapsgs05@naver.com</t>
+          <t>gymbay_@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1303-2584</t>
+          <t>0507-1469-8246</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 경명대로 1048 동성빌딩 B1층 랩스휘트니스 계산역점</t>
+          <t>인천광역시 계양구 경명대로 1056 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rapsgs05</t>
+          <t>https://blog.naver.com/gymbay_</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>599</v>
+        <v>1227</v>
       </c>
       <c r="Q5" t="n">
-        <v>2725</v>
+        <v>1504</v>
       </c>
       <c r="R5" t="n">
-        <v>3324</v>
+        <v>2731</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +918,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>37060444</t>
+          <t>1227837861</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37060444</t>
+          <t>https://m.place.naver.com/place/1227837861</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>올나잇 피트니스 헬스&amp;PT 작전점</t>
+          <t>스포닷 헬스&amp;PT&amp;G.X&amp;골프연습장&amp;테니스레슨 작전점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>all_night_b@naver.com</t>
+          <t>spodot2025@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1496-8948</t>
+          <t>0507-1390-7306</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 주부토로 372 금영프라자 5층 올나잇피트니스</t>
+          <t>인천광역시 계양구 아나지로 306 키위타워 B1,2</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/all.night_2</t>
+          <t>https://blog.naver.com/spodot2025</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1053</v>
+        <v>1651</v>
       </c>
       <c r="Q6" t="n">
-        <v>641</v>
+        <v>765</v>
       </c>
       <c r="R6" t="n">
-        <v>1694</v>
+        <v>2416</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,56 +1012,56 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1294236033</t>
+          <t>1920881664</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1294236033</t>
+          <t>https://m.place.naver.com/place/1920881664</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>인싸짐 계산점 헬스 PT</t>
+          <t>머슬라운지 PT헬스 작전점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mukiwihaeundoung@naver.com</t>
+          <t>sleekboost_gyesan@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1378-3818</t>
+          <t>0507-1363-5765</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 계양대로 147 부평농협 교대역지점 2층</t>
+          <t>인천광역시 계양구 장제로 714 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/inssagym_pay?igsh=Zzgya21hNGR3N3g3</t>
+          <t>http://pf.kakao.com/_xepxhxlG</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>751</v>
+        <v>2046</v>
       </c>
       <c r="Q7" t="n">
-        <v>2480</v>
+        <v>860</v>
       </c>
       <c r="R7" t="n">
-        <v>3231</v>
+        <v>2906</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1106,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1524298359</t>
+          <t>1138840244</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1524298359</t>
+          <t>https://m.place.naver.com/place/1138840244</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>어테인휘트니스 헬스&amp;PT 계산점</t>
+          <t>231 필라테스 &amp; 헬스PT 계산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>attainfitness_2@naver.com</t>
+          <t>jibang8316@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1337-1434</t>
+          <t>0507-1410-0161</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 계산새로 1 제2동 3층</t>
+          <t>인천광역시 계양구 계산로 148 6층 231 필라테스 &amp; 헬스PT 계산점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/attain.fitness2/</t>
+          <t>https://blog.naver.com/jibang8316</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1176,22 +1176,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>422</v>
+        <v>233</v>
       </c>
       <c r="Q8" t="n">
-        <v>1302</v>
+        <v>20</v>
       </c>
       <c r="R8" t="n">
-        <v>1724</v>
+        <v>253</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,56 +1200,56 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1018433018</t>
+          <t>1028285129</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1018433018</t>
+          <t>https://m.place.naver.com/place/1028285129</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>센스짐24작전점 연중무휴 헬스장&amp;PT</t>
+          <t>포텐핏 헬스&amp;PT 계산역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sensegym@naver.com</t>
+          <t>fitsehun@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1368-6933</t>
+          <t>0507-1362-9195</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 장제로 672 광평프라자5층 센스짐24작전점입니다</t>
+          <t>인천광역시 계양구 경명대로 1054 2층 포텐핏</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://litt.ly/sensegym_plan</t>
+          <t>https://www.instagram.com/potenfit_</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2444</v>
+        <v>107</v>
       </c>
       <c r="Q9" t="n">
-        <v>682</v>
+        <v>143</v>
       </c>
       <c r="R9" t="n">
-        <v>3126</v>
+        <v>250</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,56 +1294,56 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1490986756</t>
+          <t>1675245225</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1490986756</t>
+          <t>https://m.place.naver.com/place/1675245225</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>231 필라테스 &amp; 헬스PT 계산점</t>
+          <t>두잇핏PT 헬스 계산점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jibang8316@naver.com</t>
+          <t>doit_fit@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1410-0161</t>
+          <t>0507-1327-6910</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 계산로 148 6층 231 필라테스 &amp; 헬스PT 계산점</t>
+          <t>인천광역시 계양구 장제로 797 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xcxivRxj</t>
+          <t>https://blog.naver.com/doit_fit</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1364,22 +1364,22 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>229</v>
+        <v>73</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>189</v>
       </c>
       <c r="R10" t="n">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1388,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1028285129</t>
+          <t>1285468206</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1028285129</t>
+          <t>https://m.place.naver.com/place/1285468206</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>두잇핏PT 헬스 계산점</t>
+          <t>랩스휘트니스 헬스 PT 계산역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>doit_fit@naver.com</t>
+          <t>rapsgs05@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1327-6910</t>
+          <t>0507-1303-2584</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 장제로 797 2층</t>
+          <t>인천광역시 계양구 경명대로 1048 동성빌딩 B1층 랩스휘트니스 계산역점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/doit_fit</t>
+          <t>https://blog.naver.com/rapsgs05</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>73</v>
+        <v>599</v>
       </c>
       <c r="Q11" t="n">
-        <v>183</v>
+        <v>2765</v>
       </c>
       <c r="R11" t="n">
-        <v>256</v>
+        <v>3364</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,51 +1482,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1285468206</t>
+          <t>37060444</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1285468206</t>
+          <t>https://m.place.naver.com/place/37060444</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>크로스핏 켈로네</t>
+          <t>달리필라테스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>crossfitchelone@naver.com</t>
+          <t>dalli_pilates@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1366-6217</t>
+          <t>0507-1365-9348</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 경명대로 1083 지하층</t>
+          <t>인천 계양구 오조산로 53 303호 (인천광역시 계양구 계산동 1080-2)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/crossfitchelone</t>
+          <t>https://blog.naver.com/dalli_pilates</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1546,10 +1546,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49k63</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1561,13 +1565,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="Q12" t="n">
-        <v>337</v>
+        <v>86</v>
       </c>
       <c r="R12" t="n">
-        <v>469</v>
+        <v>162</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,115 +1580,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1088569503</t>
+          <t>1778615437</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088569503</t>
+          <t>https://m.place.naver.com/place/1778615437</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>달리필라테스</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>dalli_pilates@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1365-9348</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>인천 계양구 오조산로 53 303호 (인천광역시 계양구 계산동 1080-2)</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/dalli_pilates</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49k63</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>76</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>86</v>
-      </c>
-      <c r="R13" t="n">
-        <v>162</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1778615437</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1778615437</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/계양구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/계양구_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="Q4" t="n">
         <v>884</v>
       </c>
       <c r="R4" t="n">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -906,10 +906,10 @@
         <v>1227</v>
       </c>
       <c r="Q5" t="n">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="R5" t="n">
-        <v>2731</v>
+        <v>2733</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -940,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포닷 헬스&amp;PT&amp;G.X&amp;골프연습장&amp;테니스레슨 작전점</t>
+          <t>머슬라운지 PT헬스 작전점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spodot2025@naver.com</t>
+          <t>sleekboost_gyesan@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1390-7306</t>
+          <t>0507-1363-5765</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 아나지로 306 키위타워 B1,2</t>
+          <t>인천광역시 계양구 장제로 714 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spodot2025</t>
+          <t>http://pf.kakao.com/_xepxhxlG</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -988,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1651</v>
+        <v>2046</v>
       </c>
       <c r="Q6" t="n">
-        <v>765</v>
+        <v>860</v>
       </c>
       <c r="R6" t="n">
-        <v>2416</v>
+        <v>2906</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1920881664</t>
+          <t>1138840244</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1920881664</t>
+          <t>https://m.place.naver.com/place/1138840244</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,34 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>머슬라운지 PT헬스 작전점</t>
+          <t>스포닷 헬스&amp;PT&amp;G.X&amp;골프연습장&amp;테니스레슨 작전점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sleekboost_gyesan@naver.com</t>
+          <t>spodot2025@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1363-5765</t>
+          <t>0507-1390-7306</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 장제로 714 6층</t>
+          <t>인천광역시 계양구 아나지로 306 키위타워 B1,2</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xepxhxlG</t>
+          <t>https://blog.naver.com/spodot2025</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2046</v>
+        <v>1651</v>
       </c>
       <c r="Q7" t="n">
-        <v>860</v>
+        <v>765</v>
       </c>
       <c r="R7" t="n">
-        <v>2906</v>
+        <v>2416</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1138840244</t>
+          <t>1920881664</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138840244</t>
+          <t>https://m.place.naver.com/place/1920881664</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1123,34 +1123,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>231 필라테스 &amp; 헬스PT 계산점</t>
+          <t>샌드짐 계산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jibang8316@naver.com</t>
+          <t>sandgym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1410-0161</t>
+          <t>0507-1370-2771</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 계산로 148 6층 231 필라테스 &amp; 헬스PT 계산점</t>
+          <t>인천광역시 계양구 경명대로 1063 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jibang8316</t>
+          <t>https://blog.naver.com/sandgym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1176,22 +1176,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>233</v>
+        <v>604</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>1157</v>
       </c>
       <c r="R8" t="n">
-        <v>253</v>
+        <v>1761</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1028285129</t>
+          <t>1722099342</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1028285129</t>
+          <t>https://m.place.naver.com/place/1722099342</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,34 +1217,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>포텐핏 헬스&amp;PT 계산역점</t>
+          <t>231 필라테스 &amp; 헬스PT 계산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fitsehun@naver.com</t>
+          <t>jibang8316@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1362-9195</t>
+          <t>0507-1410-0161</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 경명대로 1054 2층 포텐핏</t>
+          <t>인천광역시 계양구 계산로 148 6층 231 필라테스 &amp; 헬스PT 계산점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/potenfit_</t>
+          <t>https://blog.naver.com/jibang8316</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1270,22 +1270,22 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>107</v>
+        <v>233</v>
       </c>
       <c r="Q9" t="n">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="R9" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1675245225</t>
+          <t>1028285129</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1675245225</t>
+          <t>https://m.place.naver.com/place/1028285129</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1316,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>두잇핏PT 헬스 계산점</t>
+          <t>포텐핏 헬스&amp;PT 계산역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>doit_fit@naver.com</t>
+          <t>fitsehun@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1327-6910</t>
+          <t>0507-1362-9195</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 장제로 797 2층</t>
+          <t>인천광역시 계양구 경명대로 1054 2층 포텐핏</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/doit_fit</t>
+          <t>https://www.instagram.com/potenfit_</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="Q10" t="n">
-        <v>189</v>
+        <v>143</v>
       </c>
       <c r="R10" t="n">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1285468206</t>
+          <t>1675245225</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1285468206</t>
+          <t>https://m.place.naver.com/place/1675245225</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1405,34 +1405,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>랩스휘트니스 헬스 PT 계산역점</t>
+          <t>두잇핏PT 헬스 계산점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rapsgs05@naver.com</t>
+          <t>doit_fit@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1303-2584</t>
+          <t>0507-1327-6910</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 경명대로 1048 동성빌딩 B1층 랩스휘트니스 계산역점</t>
+          <t>인천광역시 계양구 장제로 797 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rapsgs05</t>
+          <t>https://blog.naver.com/doit_fit</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>599</v>
+        <v>73</v>
       </c>
       <c r="Q11" t="n">
-        <v>2765</v>
+        <v>189</v>
       </c>
       <c r="R11" t="n">
-        <v>3364</v>
+        <v>262</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,113 +1482,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>37060444</t>
+          <t>1285468206</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37060444</t>
+          <t>https://m.place.naver.com/place/1285468206</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>달리필라테스</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>dalli_pilates@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1365-9348</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>인천 계양구 오조산로 53 303호 (인천광역시 계양구 계산동 1080-2)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/dalli_pilates</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49k63</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>76</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>86</v>
-      </c>
-      <c r="R12" t="n">
-        <v>162</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1778615437</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1778615437</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/계양구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/계양구_헬스장.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
     <col width="37" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 귤현길 5 2층</t>
+          <t>인천 계양구 귤현길 5 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzj9dyy</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -1128,34 +1132,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>샌드짐 계산점</t>
+          <t>센스짐24작전점 연중무휴 헬스장&amp;PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sandgym@naver.com</t>
+          <t>sensegym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1370-2771</t>
+          <t>0507-1368-6933</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 경명대로 1063 3층</t>
+          <t>인천 계양구 장제로 672 광평프라자5층 센스짐24작전점입니다</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sandgym</t>
+          <t>https://litt.ly/sensegym_plan</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,15 +1169,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44aeu</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>604</v>
+        <v>2464</v>
       </c>
       <c r="Q8" t="n">
-        <v>1157</v>
+        <v>683</v>
       </c>
       <c r="R8" t="n">
-        <v>1761</v>
+        <v>3147</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1208,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1722099342</t>
+          <t>1490986756</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722099342</t>
+          <t>https://m.place.naver.com/place/1490986756</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,34 +1225,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>231 필라테스 &amp; 헬스PT 계산점</t>
+          <t>바디플라워 계양구청점 헬스 PT 재활 체형교정</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jibang8316@naver.com</t>
+          <t>bodyflower@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1410-0161</t>
+          <t>0507-1312-9682</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 계산로 148 6층 231 필라테스 &amp; 헬스PT 계산점</t>
+          <t>인천 계양구 계산새로87번길 6 레드몰 2차 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jibang8316</t>
+          <t>https://blog.naver.com/bodyflower</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1264,28 +1272,32 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc4hit</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>233</v>
+        <v>109</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>843</v>
       </c>
       <c r="R9" t="n">
-        <v>253</v>
+        <v>952</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1306,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1028285129</t>
+          <t>933633163</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1028285129</t>
+          <t>https://m.place.naver.com/place/933633163</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1311,34 +1323,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>포텐핏 헬스&amp;PT 계산역점</t>
+          <t>231 필라테스 &amp; 헬스PT 계산점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fitsehun@naver.com</t>
+          <t>jibang8316@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1362-9195</t>
+          <t>0507-1410-0161</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 경명대로 1054 2층 포텐핏</t>
+          <t>인천 계양구 계산로 148 6층 231 필라테스 &amp; 헬스PT 계산점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/potenfit_</t>
+          <t>https://blog.naver.com/jibang8316</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,33 +1365,37 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ap97</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>107</v>
+        <v>233</v>
       </c>
       <c r="Q10" t="n">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1404,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1675245225</t>
+          <t>1028285129</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1675245225</t>
+          <t>https://m.place.naver.com/place/1028285129</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1410,29 +1426,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>두잇핏PT 헬스 계산점</t>
+          <t>포텐핏 헬스&amp;PT 계산역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>doit_fit@naver.com</t>
+          <t>fitsehun@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1327-6910</t>
+          <t>0507-1362-9195</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 장제로 797 2층</t>
+          <t>인천 계양구 경명대로 1054 2층 포텐핏</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/doit_fit</t>
+          <t>https://www.instagram.com/potenfit_</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,15 +1463,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5uttj</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1467,13 +1487,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="Q11" t="n">
-        <v>189</v>
+        <v>143</v>
       </c>
       <c r="R11" t="n">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1502,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1285468206</t>
+          <t>1675245225</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1285468206</t>
+          <t>https://m.place.naver.com/place/1675245225</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/계양구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/계양구_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
     <col width="37" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q2" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="R2" t="n">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>그린짐</t>
+          <t>와이투짐 계양점 헬스 PT 골프 필라테스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>green_gym@naver.com</t>
+          <t>y2gym12@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1482-4423</t>
+          <t>0507-1396-2001</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부평북로 339 2층</t>
+          <t>인천광역시 계양구 임학동로 38 와이투짐 계양점 24시</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/green_gym</t>
+          <t>https://open.kakao.com/o/sThOVtmh</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>321</v>
+        <v>856</v>
       </c>
       <c r="Q3" t="n">
-        <v>822</v>
+        <v>855</v>
       </c>
       <c r="R3" t="n">
-        <v>1143</v>
+        <v>1711</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +730,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1527477204</t>
+          <t>36208586</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1527477204</t>
+          <t>https://m.place.naver.com/place/36208586</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>와이투짐 계양점 헬스 PT 골프 필라테스</t>
+          <t>테이스트피트니스 헬스&amp;PT 24시 계양구청점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>y2gym12@naver.com</t>
+          <t>tastegy@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1396-2001</t>
+          <t>0507-1460-0265</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 임학동로 38 와이투짐 계양점 24시</t>
+          <t>인천광역시 계양구 오조산로57번길 7 성림프라자 6층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sThOVtmh</t>
+          <t>http://pf.kakao.com/_fbwxbn</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>853</v>
+        <v>2073</v>
       </c>
       <c r="Q4" t="n">
-        <v>852</v>
+        <v>274</v>
       </c>
       <c r="R4" t="n">
-        <v>1705</v>
+        <v>2347</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,56 +824,56 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>36208586</t>
+          <t>1987764939</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36208586</t>
+          <t>https://m.place.naver.com/place/1987764939</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>테이스트피트니스 헬스&amp;PT 24시 계양구청점</t>
+          <t>짐710 헬스장 PT 계양구청점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>tastegy@naver.com</t>
+          <t>junwon092300@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1460-0265</t>
+          <t>0507-1444-9971</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 오조산로57번길 7 성림프라자 6층</t>
+          <t>인천광역시 계양구 오조산로 53 미소지움메디칼빌딩 6층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_fbwxbn</t>
+          <t>https://blog.naver.com/junwon092300</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2073</v>
+        <v>1011</v>
       </c>
       <c r="Q5" t="n">
-        <v>274</v>
+        <v>888</v>
       </c>
       <c r="R5" t="n">
-        <v>2347</v>
+        <v>1899</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +918,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1987764939</t>
+          <t>1400484331</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1987764939</t>
+          <t>https://m.place.naver.com/place/1400484331</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>짐710 헬스장 PT 계양구청점</t>
+          <t>짐베이피트니스 헬스 PT 계산역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>junwon092300@naver.com</t>
+          <t>gymbay_@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1444-9971</t>
+          <t>0507-1469-8246</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 오조산로 53 미소지움메디칼빌딩 6층</t>
+          <t>인천광역시 계양구 경명대로 1056 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/junwon092300</t>
+          <t>https://blog.naver.com/gymbay_</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1011</v>
+        <v>1229</v>
       </c>
       <c r="Q6" t="n">
-        <v>886</v>
+        <v>1519</v>
       </c>
       <c r="R6" t="n">
-        <v>1897</v>
+        <v>2748</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1400484331</t>
+          <t>1227837861</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1400484331</t>
+          <t>https://m.place.naver.com/place/1227837861</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1034,34 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>짐베이피트니스 헬스 PT 계산역점</t>
+          <t>머슬라운지 PT헬스 작전점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gymbay_@naver.com</t>
+          <t>sleekboost_gyesan@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1469-8246</t>
+          <t>0507-1363-5765</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 경명대로 1056 5층</t>
+          <t>인천광역시 계양구 장제로 714 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymbay_</t>
+          <t>http://pf.kakao.com/_xepxhxlG</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1227</v>
+        <v>2048</v>
       </c>
       <c r="Q7" t="n">
-        <v>1511</v>
+        <v>862</v>
       </c>
       <c r="R7" t="n">
-        <v>2738</v>
+        <v>2910</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1227837861</t>
+          <t>1138840244</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1227837861</t>
+          <t>https://m.place.naver.com/place/1138840244</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1128,34 +1128,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>머슬라운지 PT헬스 작전점</t>
+          <t>스포닷 헬스&amp;PT&amp;G.X&amp;골프연습장&amp;테니스레슨 작전점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sleekboost_gyesan@naver.com</t>
+          <t>spodot2025@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1363-5765</t>
+          <t>0507-1390-7306</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 장제로 714 6층</t>
+          <t>인천광역시 계양구 아나지로 306 키위타워 B1,2</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xepxhxlG</t>
+          <t>https://blog.naver.com/spodot2025</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1176,7 +1176,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2047</v>
+        <v>1651</v>
       </c>
       <c r="Q8" t="n">
-        <v>862</v>
+        <v>770</v>
       </c>
       <c r="R8" t="n">
-        <v>2909</v>
+        <v>2421</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1200,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1138840244</t>
+          <t>1920881664</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138840244</t>
+          <t>https://m.place.naver.com/place/1920881664</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>스포닷 헬스&amp;PT&amp;G.X&amp;골프연습장&amp;테니스레슨 작전점</t>
+          <t>샌드짐 계산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>spodot2025@naver.com</t>
+          <t>sandgym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1390-7306</t>
+          <t>0507-1370-2771</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 아나지로 306 키위타워 B1,2</t>
+          <t>인천광역시 계양구 경명대로 1063 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spodot2025</t>
+          <t>https://blog.naver.com/sandgym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1651</v>
+        <v>605</v>
       </c>
       <c r="Q9" t="n">
-        <v>765</v>
+        <v>1157</v>
       </c>
       <c r="R9" t="n">
-        <v>2416</v>
+        <v>1762</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1920881664</t>
+          <t>1722099342</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1920881664</t>
+          <t>https://m.place.naver.com/place/1722099342</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1316,34 +1316,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>샌드짐 계산점</t>
+          <t>센스짐24작전점 연중무휴 헬스장&amp;PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sandgym@naver.com</t>
+          <t>sensegym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1370-2771</t>
+          <t>0507-1368-6933</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 경명대로 1063 3층</t>
+          <t>인천 계양구 장제로 672 광평프라자5층 센스짐24작전점입니다</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sandgym</t>
+          <t>https://litt.ly/sensegym_plan</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1353,15 +1353,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44aeu</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1373,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>605</v>
+        <v>2466</v>
       </c>
       <c r="Q10" t="n">
-        <v>1157</v>
+        <v>685</v>
       </c>
       <c r="R10" t="n">
-        <v>1762</v>
+        <v>3151</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1392,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1722099342</t>
+          <t>1490986756</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722099342</t>
+          <t>https://m.place.naver.com/place/1490986756</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>바디플라워 계양구청점 헬스 PT 재활 체형교정</t>
+          <t>231 필라테스 &amp; 헬스PT 계산점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bodyflower@naver.com</t>
+          <t>jibang8316@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1312-9682</t>
+          <t>0507-1410-0161</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 계산새로87번길 6 레드몰 2차 4층</t>
+          <t>인천 계양구 계산로 148 6층 231 필라테스 &amp; 헬스PT 계산점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyflower</t>
+          <t>https://blog.naver.com/jibang8316</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1452,28 +1456,32 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ap97</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>109</v>
+        <v>233</v>
       </c>
       <c r="Q11" t="n">
-        <v>843</v>
+        <v>22</v>
       </c>
       <c r="R11" t="n">
-        <v>952</v>
+        <v>255</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1490,107 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>933633163</t>
+          <t>1028285129</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/933633163</t>
+          <t>https://m.place.naver.com/place/1028285129</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>포텐핏 헬스&amp;PT 계산역점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>fitsehun@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>인천광역시 계양구 경명대로 1054 2층 포텐핏</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/potenfit_</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>139</v>
+      </c>
+      <c r="R12" t="n">
+        <v>246</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1675245225</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1675245225</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
